--- a/backtest_runs/20260410_193731/by_symbol/ARUJ/ARUJ.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/ARUJ/ARUJ.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-5090.819999999999</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>94909.18000000001</v>
@@ -633,7 +633,7 @@
         <v>-11393.73999999999</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>83515.44</v>
@@ -771,7 +771,7 @@
         <v>-3636.300000000009</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>89091.09999999999</v>
@@ -863,7 +863,7 @@
         <v>-11151.32</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>80970.03</v>
@@ -909,7 +909,7 @@
         <v>-363.6299999999923</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>80606.39999999999</v>
@@ -955,7 +955,7 @@
         <v>-2666.620000000008</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>77939.78</v>
@@ -1047,7 +1047,7 @@
         <v>-6666.550000000008</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>75879.20999999999</v>
@@ -1185,7 +1185,7 @@
         <v>-4363.559999999993</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>79030.67</v>
@@ -1369,7 +1369,7 @@
         <v>-242.4199999999948</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>87515.37000000001</v>
@@ -1415,7 +1415,7 @@
         <v>-6424.130000000014</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>81091.23999999999</v>
@@ -1461,7 +1461,7 @@
         <v>-5575.659999999989</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>75515.58</v>
